--- a/evaluation/gemini_pet.xlsx
+++ b/evaluation/gemini_pet.xlsx
@@ -333,7 +333,7 @@
     <col width="8.8" min="1" max="1" bestFit="1" customWidth="1"/>
     <col width="5.5" min="2" max="2" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -349,7 +349,7 @@
         <v>0.06117291253740876</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.07142857142857145</v>
+        <v>0.5210084033613446</v>
       </c>
     </row>
     <row r="2">
@@ -365,7 +365,7 @@
         <v>0.0</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.16666666666666666</v>
+        <v>0.5654761904761905</v>
       </c>
     </row>
     <row r="3">
@@ -381,7 +381,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4">
@@ -397,7 +397,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.0</v>
+        <v>0.4666666666666667</v>
       </c>
     </row>
     <row r="5">
@@ -413,7 +413,7 @@
         <v>0.684801817253627</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9166666666666667</v>
       </c>
     </row>
     <row r="6">
@@ -429,7 +429,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>0.0</v>
+        <v>0.46296296296296297</v>
       </c>
     </row>
     <row r="7">
@@ -445,7 +445,7 @@
         <v>0.16464091807931003</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.2253968253968254</v>
+        <v>0.6126984126984127</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>0.13944303250516168</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0.09166666666666667</v>
+        <v>0.5201923076923076</v>
       </c>
     </row>
     <row r="11">
@@ -509,7 +509,7 @@
         <v>0.3089303090858115</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.29797979797979796</v>
+        <v>0.648989898989899</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>0.14638763515159098</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.6574074074074074</v>
       </c>
     </row>
     <row r="13">
@@ -541,7 +541,7 @@
         <v>0.758306263925723</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.9444444444444444</v>
       </c>
     </row>
     <row r="14">
@@ -557,7 +557,7 @@
         <v>0.616350423579598</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="15">
@@ -573,7 +573,7 @@
         <v>0.39884258442619513</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>0.33333333333333337</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="16">
@@ -589,7 +589,7 @@
         <v>0.0</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>0.0</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="17">
@@ -605,7 +605,7 @@
         <v>0.10976690439199387</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>0.1428571428571429</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="18">
@@ -621,7 +621,7 @@
         <v>0.08928337394919182</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.5155172413793103</v>
       </c>
     </row>
     <row r="19">
@@ -657,7 +657,7 @@
         <v>0.05006166716065365</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>0.14180779531272109</v>
+        <v>0.5445881081826763</v>
       </c>
     </row>
     <row r="21">
@@ -673,7 +673,7 @@
         <v>0.16734147039698832</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>0.19999999999999996</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="22">
@@ -705,7 +705,7 @@
         <v>0.15597223800794244</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>0.06862745098039216</v>
+        <v>0.4046840958605664</v>
       </c>
     </row>
     <row r="24">
@@ -721,7 +721,7 @@
         <v>0.131913162402234</v>
       </c>
       <c r="D24" s="0" t="n">
-        <v>0.4038461538461539</v>
+        <v>0.6447802197802198</v>
       </c>
     </row>
     <row r="25">
@@ -737,7 +737,7 @@
         <v>0.2516476255442883</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>0.2341269841269841</v>
+        <v>0.5503968253968254</v>
       </c>
     </row>
     <row r="26">
@@ -769,7 +769,7 @@
         <v>0.25215960190956377</v>
       </c>
       <c r="D27" s="0" t="n">
-        <v>0.3541666666666667</v>
+        <v>0.6770833333333334</v>
       </c>
     </row>
     <row r="28">
@@ -785,7 +785,7 @@
         <v>0.31276745021304353</v>
       </c>
       <c r="D28" s="0" t="n">
-        <v>0.6193067022956136</v>
+        <v>0.8096533511478068</v>
       </c>
     </row>
     <row r="29">
@@ -801,7 +801,7 @@
         <v>0.5493559589963435</v>
       </c>
       <c r="D29" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333333</v>
       </c>
     </row>
     <row r="30">
@@ -817,7 +817,7 @@
         <v>0.0</v>
       </c>
       <c r="D30" s="0" t="n">
-        <v>0.16666666666666669</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="31">
@@ -833,7 +833,7 @@
         <v>0.16612051124024355</v>
       </c>
       <c r="D31" s="0" t="n">
-        <v>0.08332025117739403</v>
+        <v>0.39582679225536366</v>
       </c>
     </row>
     <row r="32">
@@ -849,7 +849,7 @@
         <v>0.2932054912454606</v>
       </c>
       <c r="D32" s="0" t="n">
-        <v>0.1986111111111111</v>
+        <v>0.5466739766081872</v>
       </c>
     </row>
     <row r="33">
@@ -865,7 +865,7 @@
         <v>0.10792480570540397</v>
       </c>
       <c r="D33" s="0" t="n">
-        <v>0.025745715782384198</v>
+        <v>0.3828728578911921</v>
       </c>
     </row>
     <row r="34">
@@ -881,7 +881,7 @@
         <v>0.45989889673063333</v>
       </c>
       <c r="D34" s="0" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="35">
@@ -897,7 +897,7 @@
         <v>0.512960276082257</v>
       </c>
       <c r="D35" s="0" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.8055555555555556</v>
       </c>
     </row>
     <row r="36">
@@ -913,7 +913,7 @@
         <v>0.30926144875469913</v>
       </c>
       <c r="D36" s="0" t="n">
-        <v>0.13281893004115228</v>
+        <v>0.5008356945287729</v>
       </c>
     </row>
     <row r="37">
@@ -929,7 +929,7 @@
         <v>0.8052834631113583</v>
       </c>
       <c r="D37" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333333</v>
       </c>
     </row>
     <row r="38">
@@ -945,7 +945,7 @@
         <v>0.7447703449404899</v>
       </c>
       <c r="D38" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="39">
@@ -961,7 +961,7 @@
         <v>0.4331390940198279</v>
       </c>
       <c r="D39" s="0" t="n">
-        <v>0.48928571428571427</v>
+        <v>0.6196428571428572</v>
       </c>
     </row>
     <row r="40">
@@ -977,7 +977,7 @@
         <v>0.4415157102135844</v>
       </c>
       <c r="D40" s="0" t="n">
-        <v>0.2833333333333333</v>
+        <v>0.49166666666666664</v>
       </c>
     </row>
     <row r="41">
@@ -993,7 +993,7 @@
         <v>0.25961432106483295</v>
       </c>
       <c r="D41" s="0" t="n">
-        <v>0.01875</v>
+        <v>0.309375</v>
       </c>
     </row>
     <row r="42">
@@ -1009,7 +1009,7 @@
         <v>0.11385999985730919</v>
       </c>
       <c r="D42" s="0" t="n">
-        <v>0.10416666666666666</v>
+        <v>0.4806547619047619</v>
       </c>
     </row>
     <row r="43">
@@ -1025,7 +1025,7 @@
         <v>0.3525585035076342</v>
       </c>
       <c r="D43" s="0" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.7222222222222222</v>
       </c>
     </row>
     <row r="44">
@@ -1041,7 +1041,7 @@
         <v>0.6190761910389654</v>
       </c>
       <c r="D44" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="45">
@@ -1057,7 +1057,7 @@
         <v>0.2313182647924195</v>
       </c>
       <c r="D45" s="0" t="n">
-        <v>0.08876488095238096</v>
+        <v>0.46829548395445136</v>
       </c>
     </row>
   </sheetData>

--- a/evaluation/gemini_pet.xlsx
+++ b/evaluation/gemini_pet.xlsx
@@ -333,7 +333,7 @@
     <col width="8.8" min="1" max="1" bestFit="1" customWidth="1"/>
     <col width="5.5" min="2" max="2" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="4" max="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -349,7 +349,7 @@
         <v>0.06117291253740876</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.5210084033613446</v>
+        <v>0.06932773109243699</v>
       </c>
     </row>
     <row r="2">
@@ -365,7 +365,7 @@
         <v>0.0</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.5654761904761905</v>
+        <v>0.1607142857142857</v>
       </c>
     </row>
     <row r="3">
@@ -381,7 +381,7 @@
         <v>0.0</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>0.5</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="4">
@@ -397,7 +397,7 @@
         <v>0.0</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="5">
@@ -413,7 +413,7 @@
         <v>0.684801817253627</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>0.9166666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="6">
@@ -429,7 +429,7 @@
         <v>0.0</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>0.46296296296296297</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="7">
@@ -445,7 +445,7 @@
         <v>0.16464091807931003</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.6126984126984127</v>
+        <v>0.2253968253968254</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>0.13944303250516168</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0.5201923076923076</v>
+        <v>0.08696581196581198</v>
       </c>
     </row>
     <row r="11">
@@ -509,7 +509,7 @@
         <v>0.3089303090858115</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.648989898989899</v>
+        <v>0.29797979797979796</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>0.14638763515159098</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.6574074074074074</v>
+        <v>0.360082304526749</v>
       </c>
     </row>
     <row r="13">
@@ -541,7 +541,7 @@
         <v>0.758306263925723</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="14">
@@ -557,7 +557,7 @@
         <v>0.616350423579598</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="15">
@@ -573,7 +573,7 @@
         <v>0.39884258442619513</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.27777777777777785</v>
       </c>
     </row>
     <row r="16">
@@ -589,7 +589,7 @@
         <v>0.0</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>0.45</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="17">
@@ -605,7 +605,7 @@
         <v>0.10976690439199387</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.1428571428571429</v>
       </c>
     </row>
     <row r="18">
@@ -621,7 +621,7 @@
         <v>0.08928337394919182</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>0.5155172413793103</v>
+        <v>0.09310344827586205</v>
       </c>
     </row>
     <row r="19">
@@ -657,7 +657,7 @@
         <v>0.05006166716065365</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>0.5445881081826763</v>
+        <v>0.13434422713836736</v>
       </c>
     </row>
     <row r="21">
@@ -673,7 +673,7 @@
         <v>0.16734147039698832</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>0.6</v>
+        <v>0.19999999999999996</v>
       </c>
     </row>
     <row r="22">
@@ -705,7 +705,7 @@
         <v>0.15597223800794244</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>0.4046840958605664</v>
+        <v>0.050835148874364564</v>
       </c>
     </row>
     <row r="24">
@@ -721,7 +721,7 @@
         <v>0.131913162402234</v>
       </c>
       <c r="D24" s="0" t="n">
-        <v>0.6447802197802198</v>
+        <v>0.35769230769230775</v>
       </c>
     </row>
     <row r="25">
@@ -737,7 +737,7 @@
         <v>0.2516476255442883</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>0.5503968253968254</v>
+        <v>0.2029100529100529</v>
       </c>
     </row>
     <row r="26">
@@ -769,7 +769,7 @@
         <v>0.25215960190956377</v>
       </c>
       <c r="D27" s="0" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.3541666666666667</v>
       </c>
     </row>
     <row r="28">
@@ -785,7 +785,7 @@
         <v>0.31276745021304353</v>
       </c>
       <c r="D28" s="0" t="n">
-        <v>0.8096533511478068</v>
+        <v>0.6193067022956136</v>
       </c>
     </row>
     <row r="29">
@@ -801,7 +801,7 @@
         <v>0.5493559589963435</v>
       </c>
       <c r="D29" s="0" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="30">
@@ -817,7 +817,7 @@
         <v>0.0</v>
       </c>
       <c r="D30" s="0" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.16666666666666669</v>
       </c>
     </row>
     <row r="31">
@@ -833,7 +833,7 @@
         <v>0.16612051124024355</v>
       </c>
       <c r="D31" s="0" t="n">
-        <v>0.39582679225536366</v>
+        <v>0.0590185112506541</v>
       </c>
     </row>
     <row r="32">
@@ -849,7 +849,7 @@
         <v>0.2932054912454606</v>
       </c>
       <c r="D32" s="0" t="n">
-        <v>0.5466739766081872</v>
+        <v>0.1777046783625731</v>
       </c>
     </row>
     <row r="33">
@@ -865,7 +865,7 @@
         <v>0.10792480570540397</v>
       </c>
       <c r="D33" s="0" t="n">
-        <v>0.3828728578911921</v>
+        <v>0.019051829678964308</v>
       </c>
     </row>
     <row r="34">
@@ -881,7 +881,7 @@
         <v>0.45989889673063333</v>
       </c>
       <c r="D34" s="0" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="35">
@@ -897,7 +897,7 @@
         <v>0.512960276082257</v>
       </c>
       <c r="D35" s="0" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.6111111111111112</v>
       </c>
     </row>
     <row r="36">
@@ -913,7 +913,7 @@
         <v>0.30926144875469913</v>
       </c>
       <c r="D36" s="0" t="n">
-        <v>0.5008356945287729</v>
+        <v>0.11540005397018148</v>
       </c>
     </row>
     <row r="37">
@@ -929,7 +929,7 @@
         <v>0.8052834631113583</v>
       </c>
       <c r="D37" s="0" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="38">
@@ -945,7 +945,7 @@
         <v>0.7447703449404899</v>
       </c>
       <c r="D38" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="39">
@@ -961,7 +961,7 @@
         <v>0.4331390940198279</v>
       </c>
       <c r="D39" s="0" t="n">
-        <v>0.6196428571428572</v>
+        <v>0.3669642857142857</v>
       </c>
     </row>
     <row r="40">
@@ -977,7 +977,7 @@
         <v>0.4415157102135844</v>
       </c>
       <c r="D40" s="0" t="n">
-        <v>0.49166666666666664</v>
+        <v>0.1983333333333333</v>
       </c>
     </row>
     <row r="41">
@@ -993,7 +993,7 @@
         <v>0.25961432106483295</v>
       </c>
       <c r="D41" s="0" t="n">
-        <v>0.309375</v>
+        <v>0.01125</v>
       </c>
     </row>
     <row r="42">
@@ -1009,7 +1009,7 @@
         <v>0.11385999985730919</v>
       </c>
       <c r="D42" s="0" t="n">
-        <v>0.4806547619047619</v>
+        <v>0.08928571428571429</v>
       </c>
     </row>
     <row r="43">
@@ -1025,7 +1025,7 @@
         <v>0.3525585035076342</v>
       </c>
       <c r="D43" s="0" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="44">
@@ -1041,7 +1041,7 @@
         <v>0.6190761910389654</v>
       </c>
       <c r="D44" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="45">
@@ -1057,7 +1057,7 @@
         <v>0.2313182647924195</v>
       </c>
       <c r="D45" s="0" t="n">
-        <v>0.46829548395445136</v>
+        <v>0.07525718167701864</v>
       </c>
     </row>
   </sheetData>
